--- a/results/figs/figure_6_b.xlsx
+++ b/results/figs/figure_6_b.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Samsung_SSD_990_PRO_2TB_Media/multiomics_mech/results/figs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81EDA3AB-E571-4241-9B7A-5A7B668C6653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97863EE0-6577-2A4E-89DE-6B4E5401AC78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{9E4C53ED-410F-DA4C-BD6B-504056AC50A0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="329">
   <si>
     <t>axis</t>
   </si>
@@ -997,9 +997,6 @@
     <t>Gpat4</t>
   </si>
   <si>
-    <t>Taz</t>
-  </si>
-  <si>
     <t>Lclat1</t>
   </si>
   <si>
@@ -1520,6 +1517,14 @@
   </si>
   <si>
     <t>Tier-3 条件性贡献者：直接调控 OPA1 功能状态；上升提示膜环境轴可能在应激调控层受损，但为避免跨轴泛应激信号污染，仅赋低权重，并需结合 Opa1/Immt 及 CL_fraction 共同判读</t>
+  </si>
+  <si>
+    <t>Tafazzin</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PA_PG_mismatch</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1574,14 +1579,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2083,7 +2085,7 @@
       <c r="G5" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5">
         <v>-1</v>
       </c>
       <c r="I5">
@@ -2261,7 +2263,7 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>328</v>
       </c>
       <c r="D11" t="s">
         <v>124</v>
@@ -2776,25 +2778,25 @@
         <v>143</v>
       </c>
       <c r="D27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E27" t="s">
+        <v>175</v>
+      </c>
+      <c r="F27" t="s">
         <v>176</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>177</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27">
+        <v>-1</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27" t="s">
         <v>178</v>
-      </c>
-      <c r="H27">
-        <v>-1</v>
-      </c>
-      <c r="I27">
-        <v>1</v>
-      </c>
-      <c r="J27" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -2808,25 +2810,25 @@
         <v>144</v>
       </c>
       <c r="D28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E28" t="s">
+        <v>179</v>
+      </c>
+      <c r="F28" t="s">
         <v>180</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>181</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28">
+        <v>-1</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28" t="s">
         <v>182</v>
-      </c>
-      <c r="H28">
-        <v>-1</v>
-      </c>
-      <c r="I28">
-        <v>1</v>
-      </c>
-      <c r="J28" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -2840,25 +2842,25 @@
         <v>145</v>
       </c>
       <c r="D29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E29" t="s">
+        <v>183</v>
+      </c>
+      <c r="F29" t="s">
         <v>184</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>185</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29">
+        <v>-1</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29" t="s">
         <v>186</v>
-      </c>
-      <c r="H29">
-        <v>-1</v>
-      </c>
-      <c r="I29">
-        <v>1</v>
-      </c>
-      <c r="J29" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -2872,25 +2874,25 @@
         <v>146</v>
       </c>
       <c r="D30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E30" t="s">
+        <v>187</v>
+      </c>
+      <c r="F30" t="s">
         <v>188</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>189</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30">
+        <v>-1</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30" t="s">
         <v>190</v>
-      </c>
-      <c r="H30">
-        <v>-1</v>
-      </c>
-      <c r="I30">
-        <v>1</v>
-      </c>
-      <c r="J30" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -2901,19 +2903,19 @@
         <v>3</v>
       </c>
       <c r="C31" t="s">
+        <v>191</v>
+      </c>
+      <c r="D31" t="s">
+        <v>173</v>
+      </c>
+      <c r="E31" t="s">
         <v>192</v>
       </c>
-      <c r="D31" t="s">
-        <v>174</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>193</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>194</v>
-      </c>
-      <c r="G31" t="s">
-        <v>195</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -2922,7 +2924,7 @@
         <v>0.5</v>
       </c>
       <c r="J31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -2933,19 +2935,19 @@
         <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D32" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E32" t="s">
+        <v>196</v>
+      </c>
+      <c r="F32" t="s">
         <v>197</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>198</v>
-      </c>
-      <c r="G32" t="s">
-        <v>199</v>
       </c>
       <c r="H32">
         <v>-1</v>
@@ -2954,7 +2956,7 @@
         <v>0.3</v>
       </c>
       <c r="J32" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -2965,28 +2967,28 @@
         <v>3</v>
       </c>
       <c r="C33" t="s">
-        <v>153</v>
+        <v>327</v>
       </c>
       <c r="D33" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E33" t="s">
+        <v>200</v>
+      </c>
+      <c r="F33" t="s">
         <v>201</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>202</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33">
+        <v>-1</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33" t="s">
         <v>203</v>
-      </c>
-      <c r="H33">
-        <v>-1</v>
-      </c>
-      <c r="I33">
-        <v>1</v>
-      </c>
-      <c r="J33" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -2997,28 +2999,28 @@
         <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E34" t="s">
+        <v>204</v>
+      </c>
+      <c r="F34" t="s">
         <v>205</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>206</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34">
+        <v>-1</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="J34" t="s">
         <v>207</v>
-      </c>
-      <c r="H34">
-        <v>-1</v>
-      </c>
-      <c r="I34">
-        <v>1</v>
-      </c>
-      <c r="J34" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -3029,19 +3031,19 @@
         <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D35" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E35" t="s">
+        <v>208</v>
+      </c>
+      <c r="F35" t="s">
         <v>209</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>210</v>
-      </c>
-      <c r="G35" t="s">
-        <v>211</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -3050,7 +3052,7 @@
         <v>0.5</v>
       </c>
       <c r="J35" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -3061,19 +3063,19 @@
         <v>3</v>
       </c>
       <c r="C36" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E36" t="s">
+        <v>212</v>
+      </c>
+      <c r="F36" t="s">
         <v>213</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>214</v>
-      </c>
-      <c r="G36" t="s">
-        <v>215</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -3082,7 +3084,7 @@
         <v>0.3</v>
       </c>
       <c r="J36" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -3093,28 +3095,28 @@
         <v>3</v>
       </c>
       <c r="C37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D37" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E37" t="s">
+        <v>216</v>
+      </c>
+      <c r="F37" t="s">
         <v>217</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>218</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="J37" t="s">
         <v>219</v>
-      </c>
-      <c r="H37">
-        <v>1</v>
-      </c>
-      <c r="I37">
-        <v>1</v>
-      </c>
-      <c r="J37" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -3125,19 +3127,19 @@
         <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D38" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E38" t="s">
+        <v>220</v>
+      </c>
+      <c r="F38" t="s">
         <v>221</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>222</v>
-      </c>
-      <c r="G38" t="s">
-        <v>223</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -3146,7 +3148,7 @@
         <v>0.7</v>
       </c>
       <c r="J38" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -3157,19 +3159,19 @@
         <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E39" t="s">
+        <v>224</v>
+      </c>
+      <c r="F39" t="s">
         <v>225</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>226</v>
-      </c>
-      <c r="G39" t="s">
-        <v>227</v>
       </c>
       <c r="H39">
         <v>1</v>
@@ -3178,7 +3180,7 @@
         <v>0.5</v>
       </c>
       <c r="J39" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -3189,19 +3191,19 @@
         <v>3</v>
       </c>
       <c r="C40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E40" t="s">
+        <v>228</v>
+      </c>
+      <c r="F40" t="s">
         <v>229</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>230</v>
-      </c>
-      <c r="G40" t="s">
-        <v>231</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -3210,7 +3212,7 @@
         <v>0.5</v>
       </c>
       <c r="J40" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -3221,28 +3223,28 @@
         <v>3</v>
       </c>
       <c r="C41" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E41" t="s">
+        <v>232</v>
+      </c>
+      <c r="F41" t="s">
         <v>233</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>234</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41">
+        <v>-1</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41" t="s">
         <v>235</v>
-      </c>
-      <c r="H41">
-        <v>-1</v>
-      </c>
-      <c r="I41">
-        <v>1</v>
-      </c>
-      <c r="J41" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -3253,28 +3255,28 @@
         <v>3</v>
       </c>
       <c r="C42" t="s">
+        <v>236</v>
+      </c>
+      <c r="D42" t="s">
+        <v>173</v>
+      </c>
+      <c r="E42" t="s">
         <v>237</v>
       </c>
-      <c r="D42" t="s">
-        <v>174</v>
-      </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>238</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>239</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42">
+        <v>-1</v>
+      </c>
+      <c r="I42">
+        <v>1</v>
+      </c>
+      <c r="J42" t="s">
         <v>240</v>
-      </c>
-      <c r="H42">
-        <v>-1</v>
-      </c>
-      <c r="I42">
-        <v>1</v>
-      </c>
-      <c r="J42" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -3285,19 +3287,19 @@
         <v>3</v>
       </c>
       <c r="C43" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D43" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E43" t="s">
+        <v>241</v>
+      </c>
+      <c r="F43" t="s">
         <v>242</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>243</v>
-      </c>
-      <c r="G43" t="s">
-        <v>244</v>
       </c>
       <c r="H43">
         <v>-1</v>
@@ -3306,7 +3308,7 @@
         <v>0.7</v>
       </c>
       <c r="J43" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -3317,28 +3319,28 @@
         <v>3</v>
       </c>
       <c r="C44" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D44" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E44" t="s">
+        <v>277</v>
+      </c>
+      <c r="F44" t="s">
         <v>278</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>279</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44">
+        <v>-1</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="J44" t="s">
         <v>280</v>
-      </c>
-      <c r="H44">
-        <v>-1</v>
-      </c>
-      <c r="I44">
-        <v>1</v>
-      </c>
-      <c r="J44" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -3349,28 +3351,28 @@
         <v>3</v>
       </c>
       <c r="C45" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D45" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E45" t="s">
+        <v>281</v>
+      </c>
+      <c r="F45" t="s">
         <v>282</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>283</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45">
+        <v>-1</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="J45" t="s">
         <v>284</v>
-      </c>
-      <c r="H45">
-        <v>-1</v>
-      </c>
-      <c r="I45">
-        <v>1</v>
-      </c>
-      <c r="J45" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -3381,28 +3383,28 @@
         <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D46" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E46" t="s">
+        <v>285</v>
+      </c>
+      <c r="F46" t="s">
         <v>286</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>287</v>
       </c>
-      <c r="G46" t="s">
+      <c r="H46">
+        <v>-1</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
+      <c r="J46" t="s">
         <v>288</v>
-      </c>
-      <c r="H46">
-        <v>-1</v>
-      </c>
-      <c r="I46">
-        <v>1</v>
-      </c>
-      <c r="J46" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -3416,25 +3418,25 @@
         <v>149</v>
       </c>
       <c r="D47" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E47" t="s">
+        <v>289</v>
+      </c>
+      <c r="F47" t="s">
         <v>290</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>291</v>
       </c>
-      <c r="G47" t="s">
+      <c r="H47">
+        <v>-1</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+      <c r="J47" t="s">
         <v>292</v>
-      </c>
-      <c r="H47">
-        <v>-1</v>
-      </c>
-      <c r="I47">
-        <v>1</v>
-      </c>
-      <c r="J47" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -3448,25 +3450,25 @@
         <v>147</v>
       </c>
       <c r="D48" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E48" t="s">
+        <v>293</v>
+      </c>
+      <c r="F48" t="s">
         <v>294</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>295</v>
       </c>
-      <c r="G48" t="s">
+      <c r="H48">
+        <v>-1</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+      <c r="J48" t="s">
         <v>296</v>
-      </c>
-      <c r="H48">
-        <v>-1</v>
-      </c>
-      <c r="I48">
-        <v>1</v>
-      </c>
-      <c r="J48" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -3477,19 +3479,19 @@
         <v>3</v>
       </c>
       <c r="C49" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E49" t="s">
+        <v>245</v>
+      </c>
+      <c r="F49" t="s">
         <v>246</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>247</v>
-      </c>
-      <c r="G49" t="s">
-        <v>248</v>
       </c>
       <c r="H49">
         <v>-1</v>
@@ -3498,7 +3500,7 @@
         <v>0.5</v>
       </c>
       <c r="J49" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -3512,16 +3514,16 @@
         <v>148</v>
       </c>
       <c r="D50" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E50" t="s">
+        <v>249</v>
+      </c>
+      <c r="F50" t="s">
         <v>250</v>
       </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>251</v>
-      </c>
-      <c r="G50" t="s">
-        <v>252</v>
       </c>
       <c r="H50">
         <v>-1</v>
@@ -3530,7 +3532,7 @@
         <v>0.5</v>
       </c>
       <c r="J50" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -3544,16 +3546,16 @@
         <v>150</v>
       </c>
       <c r="D51" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E51" t="s">
+        <v>253</v>
+      </c>
+      <c r="F51" t="s">
         <v>254</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>255</v>
-      </c>
-      <c r="G51" t="s">
-        <v>256</v>
       </c>
       <c r="H51">
         <v>-1</v>
@@ -3562,7 +3564,7 @@
         <v>0.5</v>
       </c>
       <c r="J51" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -3576,16 +3578,16 @@
         <v>151</v>
       </c>
       <c r="D52" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E52" t="s">
+        <v>257</v>
+      </c>
+      <c r="F52" t="s">
         <v>258</v>
       </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>259</v>
-      </c>
-      <c r="G52" t="s">
-        <v>260</v>
       </c>
       <c r="H52">
         <v>-1</v>
@@ -3594,7 +3596,7 @@
         <v>0.3</v>
       </c>
       <c r="J52" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -3608,16 +3610,16 @@
         <v>152</v>
       </c>
       <c r="D53" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E53" t="s">
+        <v>261</v>
+      </c>
+      <c r="F53" t="s">
         <v>262</v>
       </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>263</v>
-      </c>
-      <c r="G53" t="s">
-        <v>264</v>
       </c>
       <c r="H53">
         <v>-1</v>
@@ -3626,7 +3628,7 @@
         <v>0.3</v>
       </c>
       <c r="J53" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -3637,19 +3639,19 @@
         <v>3</v>
       </c>
       <c r="C54" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D54" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E54" t="s">
+        <v>265</v>
+      </c>
+      <c r="F54" t="s">
         <v>266</v>
       </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>267</v>
-      </c>
-      <c r="G54" t="s">
-        <v>268</v>
       </c>
       <c r="H54">
         <v>-1</v>
@@ -3658,7 +3660,7 @@
         <v>0.5</v>
       </c>
       <c r="J54" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -3669,19 +3671,19 @@
         <v>3</v>
       </c>
       <c r="C55" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E55" t="s">
+        <v>269</v>
+      </c>
+      <c r="F55" t="s">
         <v>270</v>
       </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>271</v>
-      </c>
-      <c r="G55" t="s">
-        <v>272</v>
       </c>
       <c r="H55">
         <v>-1</v>
@@ -3690,7 +3692,7 @@
         <v>0.3</v>
       </c>
       <c r="J55" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -3701,19 +3703,19 @@
         <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D56" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E56" t="s">
+        <v>273</v>
+      </c>
+      <c r="F56" t="s">
         <v>274</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
         <v>275</v>
-      </c>
-      <c r="G56" t="s">
-        <v>276</v>
       </c>
       <c r="H56">
         <v>-1</v>
@@ -3722,7 +3724,7 @@
         <v>0.5</v>
       </c>
       <c r="J56" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -3733,28 +3735,28 @@
         <v>3</v>
       </c>
       <c r="C57" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D57" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E57" t="s">
+        <v>297</v>
+      </c>
+      <c r="F57" t="s">
         <v>298</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>299</v>
       </c>
-      <c r="G57" t="s">
+      <c r="H57">
+        <v>-1</v>
+      </c>
+      <c r="I57">
+        <v>1</v>
+      </c>
+      <c r="J57" t="s">
         <v>300</v>
-      </c>
-      <c r="H57">
-        <v>-1</v>
-      </c>
-      <c r="I57">
-        <v>1</v>
-      </c>
-      <c r="J57" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -3765,28 +3767,28 @@
         <v>3</v>
       </c>
       <c r="C58" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D58" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E58" t="s">
+        <v>301</v>
+      </c>
+      <c r="F58" t="s">
         <v>302</v>
       </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
         <v>303</v>
       </c>
-      <c r="G58" t="s">
+      <c r="H58">
+        <v>-1</v>
+      </c>
+      <c r="I58">
+        <v>1</v>
+      </c>
+      <c r="J58" t="s">
         <v>304</v>
-      </c>
-      <c r="H58">
-        <v>-1</v>
-      </c>
-      <c r="I58">
-        <v>1</v>
-      </c>
-      <c r="J58" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -3797,19 +3799,19 @@
         <v>3</v>
       </c>
       <c r="C59" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D59" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E59" t="s">
+        <v>305</v>
+      </c>
+      <c r="F59" t="s">
         <v>306</v>
       </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
         <v>307</v>
-      </c>
-      <c r="G59" t="s">
-        <v>308</v>
       </c>
       <c r="H59">
         <v>-1</v>
@@ -3818,7 +3820,7 @@
         <v>0.7</v>
       </c>
       <c r="J59" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -3829,19 +3831,19 @@
         <v>3</v>
       </c>
       <c r="C60" t="s">
+        <v>309</v>
+      </c>
+      <c r="D60" t="s">
+        <v>173</v>
+      </c>
+      <c r="E60" t="s">
         <v>310</v>
       </c>
-      <c r="D60" t="s">
-        <v>174</v>
-      </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>311</v>
       </c>
-      <c r="F60" t="s">
+      <c r="G60" t="s">
         <v>312</v>
-      </c>
-      <c r="G60" t="s">
-        <v>313</v>
       </c>
       <c r="H60">
         <v>-1</v>
@@ -3850,7 +3852,7 @@
         <v>0.5</v>
       </c>
       <c r="J60" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -3861,19 +3863,19 @@
         <v>3</v>
       </c>
       <c r="C61" t="s">
+        <v>172</v>
+      </c>
+      <c r="D61" t="s">
         <v>173</v>
       </c>
-      <c r="D61" t="s">
-        <v>174</v>
-      </c>
       <c r="E61" t="s">
+        <v>314</v>
+      </c>
+      <c r="F61" t="s">
         <v>315</v>
       </c>
-      <c r="F61" t="s">
+      <c r="G61" t="s">
         <v>316</v>
-      </c>
-      <c r="G61" t="s">
-        <v>317</v>
       </c>
       <c r="H61">
         <v>-1</v>
@@ -3882,7 +3884,7 @@
         <v>0.5</v>
       </c>
       <c r="J61" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -3893,19 +3895,19 @@
         <v>3</v>
       </c>
       <c r="C62" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D62" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E62" t="s">
+        <v>318</v>
+      </c>
+      <c r="F62" t="s">
         <v>319</v>
       </c>
-      <c r="F62" t="s">
+      <c r="G62" t="s">
         <v>320</v>
-      </c>
-      <c r="G62" t="s">
-        <v>321</v>
       </c>
       <c r="H62">
         <v>-1</v>
@@ -3914,7 +3916,7 @@
         <v>0.3</v>
       </c>
       <c r="J62" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="63" spans="1:10">
@@ -3925,19 +3927,19 @@
         <v>3</v>
       </c>
       <c r="C63" t="s">
+        <v>322</v>
+      </c>
+      <c r="D63" t="s">
+        <v>173</v>
+      </c>
+      <c r="E63" t="s">
         <v>323</v>
       </c>
-      <c r="D63" t="s">
-        <v>174</v>
-      </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>324</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>325</v>
-      </c>
-      <c r="G63" t="s">
-        <v>326</v>
       </c>
       <c r="H63">
         <v>1</v>
@@ -3946,7 +3948,7 @@
         <v>0.3</v>
       </c>
       <c r="J63" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
